--- a/artfynd/A 29455-2021 artfynd.xlsx
+++ b/artfynd/A 29455-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 29455-2021 artfynd.xlsx
+++ b/artfynd/A 29455-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -797,6 +797,325 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129003439</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57880</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>A 29455, Simondal, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>570964</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6422638</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129003553</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91927</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5420</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Grovticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Phaeolus schweinitzii</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>A 29455, Simondal, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>570950</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6422685</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129003460</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79124</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>A 29455, Simondal, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>570943</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6422642</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29455-2021 artfynd.xlsx
+++ b/artfynd/A 29455-2021 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>129003439</v>
       </c>
       <c r="B3" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>129003553</v>
       </c>
       <c r="B4" t="n">
-        <v>91927</v>
+        <v>91932</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>129003460</v>
       </c>
       <c r="B5" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 29455-2021 artfynd.xlsx
+++ b/artfynd/A 29455-2021 artfynd.xlsx
@@ -909,36 +909,44 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129003460</v>
+        <v>129003553</v>
       </c>
       <c r="B4" t="n">
-        <v>79034</v>
+        <v>91943</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5420</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -947,10 +955,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570943</v>
+        <v>570950</v>
       </c>
       <c r="R4" t="n">
-        <v>6422642</v>
+        <v>6422685</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1010,44 +1018,36 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129003553</v>
+        <v>129003460</v>
       </c>
       <c r="B5" t="n">
-        <v>91940</v>
+        <v>79034</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5420</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570950</v>
+        <v>570943</v>
       </c>
       <c r="R5" t="n">
-        <v>6422685</v>
+        <v>6422642</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 29455-2021 artfynd.xlsx
+++ b/artfynd/A 29455-2021 artfynd.xlsx
@@ -912,7 +912,7 @@
         <v>129003553</v>
       </c>
       <c r="B4" t="n">
-        <v>91943</v>
+        <v>91946</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>129003460</v>
       </c>
       <c r="B5" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 29455-2021 artfynd.xlsx
+++ b/artfynd/A 29455-2021 artfynd.xlsx
@@ -909,44 +909,36 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129003553</v>
+        <v>129003460</v>
       </c>
       <c r="B4" t="n">
-        <v>91946</v>
+        <v>79035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5420</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -955,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570950</v>
+        <v>570943</v>
       </c>
       <c r="R4" t="n">
-        <v>6422685</v>
+        <v>6422642</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1018,36 +1010,44 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129003460</v>
+        <v>129003553</v>
       </c>
       <c r="B5" t="n">
-        <v>79035</v>
+        <v>91946</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5420</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570943</v>
+        <v>570950</v>
       </c>
       <c r="R5" t="n">
-        <v>6422642</v>
+        <v>6422685</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 29455-2021 artfynd.xlsx
+++ b/artfynd/A 29455-2021 artfynd.xlsx
@@ -909,36 +909,44 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129003460</v>
+        <v>129003553</v>
       </c>
       <c r="B4" t="n">
-        <v>79035</v>
+        <v>91946</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5420</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -947,10 +955,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570943</v>
+        <v>570950</v>
       </c>
       <c r="R4" t="n">
-        <v>6422642</v>
+        <v>6422685</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1010,44 +1018,36 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129003553</v>
+        <v>129003460</v>
       </c>
       <c r="B5" t="n">
-        <v>91946</v>
+        <v>79035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5420</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570950</v>
+        <v>570943</v>
       </c>
       <c r="R5" t="n">
-        <v>6422685</v>
+        <v>6422642</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 29455-2021 artfynd.xlsx
+++ b/artfynd/A 29455-2021 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>129003439</v>
       </c>
       <c r="B3" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,36 +909,44 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129003460</v>
+        <v>129003553</v>
       </c>
       <c r="B4" t="n">
-        <v>79035</v>
+        <v>91953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5420</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -947,10 +955,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570943</v>
+        <v>570950</v>
       </c>
       <c r="R4" t="n">
-        <v>6422642</v>
+        <v>6422685</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1010,44 +1018,36 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129003553</v>
+        <v>129003460</v>
       </c>
       <c r="B5" t="n">
-        <v>91946</v>
+        <v>79039</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5420</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570950</v>
+        <v>570943</v>
       </c>
       <c r="R5" t="n">
-        <v>6422685</v>
+        <v>6422642</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 29455-2021 artfynd.xlsx
+++ b/artfynd/A 29455-2021 artfynd.xlsx
@@ -912,7 +912,7 @@
         <v>129003553</v>
       </c>
       <c r="B4" t="n">
-        <v>91953</v>
+        <v>91960</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 29455-2021 artfynd.xlsx
+++ b/artfynd/A 29455-2021 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>129003439</v>
       </c>
       <c r="B3" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>129003553</v>
       </c>
       <c r="B4" t="n">
-        <v>91960</v>
+        <v>91962</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>129003460</v>
       </c>
       <c r="B5" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 29455-2021 artfynd.xlsx
+++ b/artfynd/A 29455-2021 artfynd.xlsx
@@ -909,44 +909,36 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129003553</v>
+        <v>129003460</v>
       </c>
       <c r="B4" t="n">
-        <v>91962</v>
+        <v>79041</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5420</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -955,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570950</v>
+        <v>570943</v>
       </c>
       <c r="R4" t="n">
-        <v>6422685</v>
+        <v>6422642</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1018,36 +1010,44 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129003460</v>
+        <v>129003553</v>
       </c>
       <c r="B5" t="n">
-        <v>79041</v>
+        <v>91962</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5420</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570943</v>
+        <v>570950</v>
       </c>
       <c r="R5" t="n">
-        <v>6422642</v>
+        <v>6422685</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 29455-2021 artfynd.xlsx
+++ b/artfynd/A 29455-2021 artfynd.xlsx
@@ -909,36 +909,44 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129003460</v>
+        <v>129003553</v>
       </c>
       <c r="B4" t="n">
-        <v>79041</v>
+        <v>91962</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5420</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -947,10 +955,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570943</v>
+        <v>570950</v>
       </c>
       <c r="R4" t="n">
-        <v>6422642</v>
+        <v>6422685</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1010,44 +1018,36 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129003553</v>
+        <v>129003460</v>
       </c>
       <c r="B5" t="n">
-        <v>91962</v>
+        <v>79041</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5420</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570950</v>
+        <v>570943</v>
       </c>
       <c r="R5" t="n">
-        <v>6422685</v>
+        <v>6422642</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 29455-2021 artfynd.xlsx
+++ b/artfynd/A 29455-2021 artfynd.xlsx
@@ -909,44 +909,36 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129003553</v>
+        <v>129003460</v>
       </c>
       <c r="B4" t="n">
-        <v>91962</v>
+        <v>79041</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5420</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -955,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570950</v>
+        <v>570943</v>
       </c>
       <c r="R4" t="n">
-        <v>6422685</v>
+        <v>6422642</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1018,36 +1010,44 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129003460</v>
+        <v>129003553</v>
       </c>
       <c r="B5" t="n">
-        <v>79041</v>
+        <v>91971</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5420</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570943</v>
+        <v>570950</v>
       </c>
       <c r="R5" t="n">
-        <v>6422642</v>
+        <v>6422685</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 29455-2021 artfynd.xlsx
+++ b/artfynd/A 29455-2021 artfynd.xlsx
@@ -1013,7 +1013,7 @@
         <v>129003553</v>
       </c>
       <c r="B5" t="n">
-        <v>91971</v>
+        <v>91972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 29455-2021 artfynd.xlsx
+++ b/artfynd/A 29455-2021 artfynd.xlsx
@@ -912,7 +912,7 @@
         <v>129003460</v>
       </c>
       <c r="B4" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>129003553</v>
       </c>
       <c r="B5" t="n">
-        <v>91972</v>
+        <v>91975</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 29455-2021 artfynd.xlsx
+++ b/artfynd/A 29455-2021 artfynd.xlsx
@@ -912,7 +912,7 @@
         <v>129003460</v>
       </c>
       <c r="B4" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>129003553</v>
       </c>
       <c r="B5" t="n">
-        <v>91975</v>
+        <v>91977</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 29455-2021 artfynd.xlsx
+++ b/artfynd/A 29455-2021 artfynd.xlsx
@@ -909,36 +909,44 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129003460</v>
+        <v>129003553</v>
       </c>
       <c r="B4" t="n">
-        <v>79044</v>
+        <v>91981</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5420</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -947,10 +955,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570943</v>
+        <v>570950</v>
       </c>
       <c r="R4" t="n">
-        <v>6422642</v>
+        <v>6422685</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1010,44 +1018,36 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129003553</v>
+        <v>129003460</v>
       </c>
       <c r="B5" t="n">
-        <v>91977</v>
+        <v>79044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5420</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570950</v>
+        <v>570943</v>
       </c>
       <c r="R5" t="n">
-        <v>6422685</v>
+        <v>6422642</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 29455-2021 artfynd.xlsx
+++ b/artfynd/A 29455-2021 artfynd.xlsx
@@ -909,44 +909,36 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129003553</v>
+        <v>129003460</v>
       </c>
       <c r="B4" t="n">
-        <v>91981</v>
+        <v>79044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5420</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -955,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570950</v>
+        <v>570943</v>
       </c>
       <c r="R4" t="n">
-        <v>6422685</v>
+        <v>6422642</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1018,36 +1010,44 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129003460</v>
+        <v>129003553</v>
       </c>
       <c r="B5" t="n">
-        <v>79044</v>
+        <v>91982</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5420</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570943</v>
+        <v>570950</v>
       </c>
       <c r="R5" t="n">
-        <v>6422642</v>
+        <v>6422685</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 29455-2021 artfynd.xlsx
+++ b/artfynd/A 29455-2021 artfynd.xlsx
@@ -909,36 +909,44 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129003460</v>
+        <v>129003553</v>
       </c>
       <c r="B4" t="n">
-        <v>79044</v>
+        <v>91982</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5420</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -947,10 +955,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570943</v>
+        <v>570950</v>
       </c>
       <c r="R4" t="n">
-        <v>6422642</v>
+        <v>6422685</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1010,44 +1018,36 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129003553</v>
+        <v>129003460</v>
       </c>
       <c r="B5" t="n">
-        <v>91982</v>
+        <v>79044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5420</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570950</v>
+        <v>570943</v>
       </c>
       <c r="R5" t="n">
-        <v>6422685</v>
+        <v>6422642</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 29455-2021 artfynd.xlsx
+++ b/artfynd/A 29455-2021 artfynd.xlsx
@@ -912,7 +912,7 @@
         <v>129003553</v>
       </c>
       <c r="B4" t="n">
-        <v>91982</v>
+        <v>91985</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
